--- a/artfynd/A 63581-2023 artfynd.xlsx
+++ b/artfynd/A 63581-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63581-2023 artfynd.xlsx
+++ b/artfynd/A 63581-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16770152</v>
+        <v>80258631</v>
       </c>
       <c r="B2" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>V Sandtorp, Srm</t>
+          <t>Sandtorp, V om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637081.9612641303</v>
+        <v>637094</v>
       </c>
       <c r="R2" t="n">
-        <v>6563273.879820645</v>
+        <v>6563275</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-10-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-10-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Granlåga.</t>
+          <t>På gammal tallåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -803,63 +782,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16770147</v>
+        <v>80259987</v>
       </c>
       <c r="B3" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>V Sandtorp, Srm</t>
+          <t>Sandtorp, V om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636991.1615158566</v>
+        <v>636876</v>
       </c>
       <c r="R3" t="n">
-        <v>6563270.10054122</v>
+        <v>6562917</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,22 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-10-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-10-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal tallåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17201726</v>
+        <v>16770152</v>
       </c>
       <c r="B4" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,25 +900,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -969,13 +935,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637137.9842060125</v>
+        <v>637082</v>
       </c>
       <c r="R4" t="n">
-        <v>6563258.972025014</v>
+        <v>6563274</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,27 +965,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog.</t>
+          <t>Granlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,22 +995,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Mikael Essmyren</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>53905258</v>
+        <v>53905191</v>
       </c>
       <c r="B5" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,36 +1013,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>V Sandtorp, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637054.097151437</v>
+        <v>636908</v>
       </c>
       <c r="R5" t="n">
-        <v>6563048.753385078</v>
+        <v>6563208</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,21 +1081,11 @@
           <t>2015-03-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-03-11</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>Granlåga.</t>
@@ -1147,7 +1097,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1166,52 +1115,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>53905209</v>
+        <v>116229616</v>
       </c>
       <c r="B6" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>S Sandtorp, Srm</t>
+          <t>Sandtorp, V om, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637043.9835709109</v>
+        <v>636941</v>
       </c>
       <c r="R6" t="n">
-        <v>6563129.937256856</v>
+        <v>6563126</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1238,27 +1183,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Granlåga i gammal barrblandskog med rikligt inslag av död ved. Nyckelbiotop.</t>
+          <t>På granlåga. Inslag av senvuxna granar med rik hänglavsflora.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,22 +1214,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Mikael Essmyren</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>53905291</v>
+        <v>16770147</v>
       </c>
       <c r="B7" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,42 +1232,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101735</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>V Sandtorp, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637170.9675564745</v>
+        <v>636991</v>
       </c>
       <c r="R7" t="n">
-        <v>6563027.828230854</v>
+        <v>6563270</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,27 +1296,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Kläckhål i fnöskticka på björkhögstubbe.</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,6 +1310,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1401,22 +1322,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Mikael Essmyren</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>53905191</v>
+        <v>53905209</v>
       </c>
       <c r="B8" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,45 +1340,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>V Sandtorp, Srm</t>
+          <t>S Sandtorp, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636908.1042854299</v>
+        <v>637044</v>
       </c>
       <c r="R8" t="n">
-        <v>6563208.135961752</v>
+        <v>6563130</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1492,24 +1399,14 @@
           <t>2015-03-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2015-03-11</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Granlåga.</t>
+          <t>Granlåga i gammal barrblandskog med rikligt inslag av död ved. Nyckelbiotop.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,6 +1415,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1536,15 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>53905274</v>
+        <v>53905258</v>
       </c>
       <c r="B9" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637066.7525830992</v>
+        <v>637054</v>
       </c>
       <c r="R9" t="n">
-        <v>6562996.894146235</v>
+        <v>6563049</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1611,24 +1504,14 @@
           <t>2015-03-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2015-03-11</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Granlåga i gammal barrblandskog med rikligt inslag av död ved. Nyckelbiotop.</t>
+          <t>Granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1656,15 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16770135</v>
+        <v>53905274</v>
       </c>
       <c r="B10" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,28 +1550,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6031</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1702,13 +1576,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637211.866938306</v>
+        <v>637067</v>
       </c>
       <c r="R10" t="n">
-        <v>6563047.765020545</v>
+        <v>6562997</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1732,22 +1606,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2014-10-21</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2014-10-21</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Granlåga i gammal barrblandskog med rikligt inslag av död ved. Nyckelbiotop.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1768,22 +1637,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Mikael Essmyren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80261481</v>
+        <v>80258726</v>
       </c>
       <c r="B11" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1818,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637112.1173191324</v>
+        <v>637003</v>
       </c>
       <c r="R11" t="n">
-        <v>6563221.11502593</v>
+        <v>6563288</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1851,19 +1715,14 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På högstubbe av gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1894,12 +1753,7 @@
         <v>80260225</v>
       </c>
       <c r="B12" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637048.1151058292</v>
+        <v>637048</v>
       </c>
       <c r="R12" t="n">
-        <v>6562900.8247158</v>
+        <v>6562901</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1967,19 +1821,9 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2012,43 +1856,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80259987</v>
+        <v>80260260</v>
       </c>
       <c r="B13" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2056,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>636875.9141547815</v>
+        <v>637100</v>
       </c>
       <c r="R13" t="n">
-        <v>6562917.201814952</v>
+        <v>6563065</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2089,24 +1927,14 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal tallåga.</t>
+          <t>På låga och högstubbe av gran. Många fynd inom biotopen. Rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,37 +1962,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>80259928</v>
+        <v>80260298</v>
       </c>
       <c r="B14" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2177,10 +2000,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636893.2233501009</v>
+        <v>637109</v>
       </c>
       <c r="R14" t="n">
-        <v>6562978.85831906</v>
+        <v>6563073</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2210,19 +2033,14 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På granlåga. Många fynd inom biotopen. Rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2250,15 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>80261404</v>
+        <v>80260723</v>
       </c>
       <c r="B15" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,21 +2079,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2293,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637058.0162395026</v>
+        <v>637098</v>
       </c>
       <c r="R15" t="n">
-        <v>6563154.034192687</v>
+        <v>6563075</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2326,24 +2139,14 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Grupp med nyligen dödade granar av granbarkborre. Rikligt med död ved.</t>
+          <t>På låga och högstubbe av gran. Många fynd inom biotopen. Rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2371,37 +2174,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>80259934</v>
+        <v>80261132</v>
       </c>
       <c r="B16" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4368</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2414,10 +2212,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636893.2233501009</v>
+        <v>637102</v>
       </c>
       <c r="R16" t="n">
-        <v>6562978.85831906</v>
+        <v>6563082</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2447,19 +2245,14 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På högstubbe av gran. Många fynd inom biotopen. Rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2487,15 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>80260156</v>
+        <v>80261436</v>
       </c>
       <c r="B17" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2503,32 +2291,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101735</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2536,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636972.2220654265</v>
+        <v>637039</v>
       </c>
       <c r="R17" t="n">
-        <v>6562910.917993622</v>
+        <v>6563182</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2569,24 +2351,14 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gnag- och kläckhål i fnöskticka på högstubbe och låga av björk.</t>
+          <t>På grannlaga. Många fynd inom biotopen. Rikligt inslag av död ved.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2614,53 +2386,47 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80258726</v>
+        <v>67977891</v>
       </c>
       <c r="B18" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1339</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sandtorp, V om, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>637002.8495321594</v>
+        <v>636992</v>
       </c>
       <c r="R18" t="n">
-        <v>6563287.957876987</v>
+        <v>6563298</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2687,27 +2453,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På högstubbe av gran.</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2735,15 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>80260018</v>
+        <v>80258734</v>
       </c>
       <c r="B19" t="n">
-        <v>56286</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2751,31 +2497,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100001</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2783,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636844.8270217107</v>
+        <v>636987</v>
       </c>
       <c r="R19" t="n">
-        <v>6562953.013653133</v>
+        <v>6563295</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2816,32 +2557,18 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>En skrikande duvhök.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2860,15 +2587,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>80261496</v>
+        <v>80259928</v>
       </c>
       <c r="B20" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2876,21 +2598,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4368</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2903,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>637157.8323592978</v>
+        <v>636893</v>
       </c>
       <c r="R20" t="n">
-        <v>6563249.94232051</v>
+        <v>6562979</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2936,24 +2658,9 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Nära stig.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2984,12 +2691,7 @@
         <v>80260013</v>
       </c>
       <c r="B21" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3024,10 +2726,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>636844.8270217107</v>
+        <v>636845</v>
       </c>
       <c r="R21" t="n">
-        <v>6562953.013653133</v>
+        <v>6562953</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3057,19 +2759,9 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3105,12 +2797,7 @@
         <v>80259720</v>
       </c>
       <c r="B22" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,10 +2832,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636935.9960940391</v>
+        <v>636936</v>
       </c>
       <c r="R22" t="n">
-        <v>6563204.009862406</v>
+        <v>6563204</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3178,19 +2865,9 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3218,61 +2895,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>80258610</v>
+        <v>80261481</v>
       </c>
       <c r="B23" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sandtorp, N om, Srm</t>
+          <t>Sandtorp, V om, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>637044.1252424294</v>
+        <v>637112</v>
       </c>
       <c r="R23" t="n">
-        <v>6563340.21459139</v>
+        <v>6563221</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3302,24 +2966,9 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På rotben av gammal tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3347,37 +2996,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>80261436</v>
+        <v>116229229</v>
       </c>
       <c r="B24" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1339</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3390,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>637039.0254425157</v>
+        <v>637057</v>
       </c>
       <c r="R24" t="n">
-        <v>6563182.071599654</v>
+        <v>6563286</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3420,27 +3064,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På grannlaga. Många fynd inom biotopen. Rikligt inslag av död ved.</t>
+          <t>Ett antal fjolårsex.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3468,15 +3102,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>80260066</v>
+        <v>80261404</v>
       </c>
       <c r="B25" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3484,21 +3113,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3511,10 +3140,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636951.9331841052</v>
+        <v>637058</v>
       </c>
       <c r="R25" t="n">
-        <v>6562917.882127805</v>
+        <v>6563154</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3544,24 +3173,14 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gren på högstubbe av gran. Rikligt med granlågor.</t>
+          <t>Grupp med nyligen dödade granar av granbarkborre. Rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3589,37 +3208,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>80260723</v>
+        <v>80259934</v>
       </c>
       <c r="B26" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1339</v>
+        <v>4368</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3632,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>637097.85439874</v>
+        <v>636893</v>
       </c>
       <c r="R26" t="n">
-        <v>6563074.946207571</v>
+        <v>6562979</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3665,24 +3279,9 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På låga och högstubbe av gran. Många fynd inom biotopen. Rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3710,15 +3309,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>80261520</v>
+        <v>80261496</v>
       </c>
       <c r="B27" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3753,10 +3347,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>637209.8687937395</v>
+        <v>637158</v>
       </c>
       <c r="R27" t="n">
-        <v>6563203.094381525</v>
+        <v>6563250</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3786,19 +3380,14 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Nära stig.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3826,37 +3415,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>80260298</v>
+        <v>80261520</v>
       </c>
       <c r="B28" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1339</v>
+        <v>4368</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3869,10 +3453,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637109.2352940768</v>
+        <v>637210</v>
       </c>
       <c r="R28" t="n">
-        <v>6563072.791387735</v>
+        <v>6563203</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3902,24 +3486,9 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På granlåga. Många fynd inom biotopen. Rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3947,15 +3516,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>80260260</v>
+        <v>80258610</v>
       </c>
       <c r="B29" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3963,37 +3527,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1339</v>
+        <v>5420</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sandtorp, V om, Srm</t>
+          <t>Sandtorp, N om, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637099.7624430445</v>
+        <v>637044</v>
       </c>
       <c r="R29" t="n">
-        <v>6563064.757237067</v>
+        <v>6563340</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4023,24 +3595,14 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På låga och högstubbe av gran. Många fynd inom biotopen. Rikligt med död ved.</t>
+          <t>På rotben av gammal tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4068,15 +3630,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>80261132</v>
+        <v>116229670</v>
       </c>
       <c r="B30" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4084,21 +3641,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4111,10 +3668,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>637102.232869098</v>
+        <v>637061</v>
       </c>
       <c r="R30" t="n">
-        <v>6563081.771229713</v>
+        <v>6562974</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4141,27 +3698,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På högstubbe av gran. Många fynd inom biotopen. Rikligt med död ved.</t>
+          <t>På granlåga. Rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4189,15 +3736,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>80258631</v>
+        <v>67977881</v>
       </c>
       <c r="B31" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4205,38 +3747,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sandtorp, V om, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>637094.257154785</v>
+        <v>637015</v>
       </c>
       <c r="R31" t="n">
-        <v>6563274.835173436</v>
+        <v>6563331</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4263,27 +3803,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gammal tallåga.</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4311,19 +3836,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>80259898</v>
+        <v>67977900</v>
       </c>
       <c r="B32" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4336,28 +3856,27 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sandtorp, V om, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>636884.2401756116</v>
+        <v>636956</v>
       </c>
       <c r="R32" t="n">
-        <v>6563000.076927732</v>
+        <v>6563294</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4384,22 +3903,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4427,53 +3936,47 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>116229229</v>
+        <v>68197106</v>
       </c>
       <c r="B33" t="n">
-        <v>91690</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sandtorp, V om, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>637057</v>
+        <v>637012</v>
       </c>
       <c r="R33" t="n">
-        <v>6563286</v>
+        <v>6563327</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4500,17 +4003,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2017-11-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ett antal fjolårsex.</t>
+          <t>2017-11-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4538,15 +4036,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>116229313</v>
+        <v>68197281</v>
       </c>
       <c r="B34" t="n">
-        <v>90808</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4554,32 +4047,36 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6040186</v>
+        <v>5964</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sandtorp, V om, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>637051</v>
+        <v>636988</v>
       </c>
       <c r="R34" t="n">
-        <v>6563197</v>
+        <v>6563297</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4606,17 +4103,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2017-11-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2017-11-01</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På granlåga. Rikligt med granlågor både gamla och nya granbarkborredödade träd.</t>
+          <t>Allmänt förekommande.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4644,37 +4141,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>116229670</v>
+        <v>80259898</v>
       </c>
       <c r="B35" t="n">
-        <v>90382</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>5964</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4687,10 +4179,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>637061</v>
+        <v>636884</v>
       </c>
       <c r="R35" t="n">
-        <v>6562974</v>
+        <v>6563000</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4717,17 +4209,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2019-10-03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På granlåga. Rikligt med död ved.</t>
+          <t>2019-10-03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4755,56 +4242,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>116229616</v>
+        <v>16770135</v>
       </c>
       <c r="B36" t="n">
-        <v>90417</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sandtorp, V om, Srm</t>
+          <t>V Sandtorp, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>636941</v>
+        <v>637212</v>
       </c>
       <c r="R36" t="n">
-        <v>6563126</v>
+        <v>6563048</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4828,17 +4313,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På granlåga. Inslag av senvuxna granar med rik hänglavsflora.</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4863,6 +4343,873 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>80260018</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57874</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sandtorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>636845</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6562953</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Nykvarn</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Turinge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2019-10-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2019-10-03</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>En skrikande duvhök.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>80259893</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sandtorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>636828</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6563040</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Nykvarn</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Turinge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2019-10-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2019-10-03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>53905291</v>
+      </c>
+      <c r="B39" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>V Sandtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>637171</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6563028</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Nykvarn</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Turinge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2015-03-11</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2015-03-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Kläckhål i fnöskticka på björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Mikael Essmyren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>80260156</v>
+      </c>
+      <c r="B40" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sandtorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>636972</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6562911</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Nykvarn</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Turinge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2019-10-03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2019-10-03</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gnag- och kläckhål i fnöskticka på högstubbe och låga av björk.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>80261563</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sandtorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>637273</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6563274</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Nykvarn</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Turinge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2019-10-03</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2019-10-03</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>68197145</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sandtorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>636918</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6563243</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Nykvarn</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Turinge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2017-11-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2017-11-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Födosökande gröngöling vid mystack.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>17201726</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>V Sandtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>637138</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6563259</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Nykvarn</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Turinge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2015-03-11</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2015-03-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Mikael Essmyren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>116229313</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sandtorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>637051</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6563197</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Nykvarn</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Turinge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På granlåga. Rikligt med granlågor både gamla och nya granbarkborredödade träd.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63581-2023 artfynd.xlsx
+++ b/artfynd/A 63581-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80258631</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80259987</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16770152</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53905191</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116229616</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16770147</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53905209</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53905258</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53905274</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80258726</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1853,6 +1908,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80260225</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1959,6 +2019,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80260260</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2065,6 +2130,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80260298</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2171,6 +2241,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80260723</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80261132</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2383,6 +2463,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80261436</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2483,6 +2568,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977891</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2584,6 +2674,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80258734</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2685,6 +2780,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80259928</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2791,6 +2891,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80260013</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2892,6 +2997,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80259720</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2993,6 +3103,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80261481</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3099,6 +3214,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116229229</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3205,6 +3325,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80261404</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3306,6 +3431,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80259934</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3412,6 +3542,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80261496</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3513,6 +3648,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80261520</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3627,6 +3767,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80258610</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3733,6 +3878,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116229670</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3833,6 +3983,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977881</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3933,6 +4088,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67977900</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4033,6 +4193,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68197106</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4138,6 +4303,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68197281</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4239,6 +4409,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80259898</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4343,6 +4518,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16770135</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4453,6 +4633,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80260018</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4560,6 +4745,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80259893</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4667,6 +4857,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53905291</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4779,6 +4974,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80260156</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4886,6 +5086,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80261563</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4999,6 +5204,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68197145</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5104,6 +5314,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17201726</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5210,8 +5425,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116229313</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>